--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_01-10-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_01-10-2025.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -780,12 +780,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.55</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.55</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£32.56</t>
+          <t>£32.39</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff70eb01eb5+80197]
-	GetHandleVerifier [0x0x7ff70eb01f10+80288]
-	(No symbol) [0x0x7ff70e8802fa]
-	(No symbol) [0x0x7ff70e8d7cd7]
-	(No symbol) [0x0x7ff70e8d7f9c]
-	(No symbol) [0x0x7ff70e92ba87]
-	(No symbol) [0x0x7ff70e9003bf]
-	(No symbol) [0x0x7ff70e9287fb]
-	(No symbol) [0x0x7ff70e900153]
-	(No symbol) [0x0x7ff70e8c8b02]
-	(No symbol) [0x0x7ff70e8c98d3]
-	GetHandleVerifier [0x0x7ff70edbe83d+2949837]
-	GetHandleVerifier [0x0x7ff70edb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff70edd86c7+3055959]
-	GetHandleVerifier [0x0x7ff70eb1cfee+191102]
-	GetHandleVerifier [0x0x7ff70eb250af+224063]
-	GetHandleVerifier [0x0x7ff70eb0af64+117236]
-	GetHandleVerifier [0x0x7ff70eb0b119+117673]
-	GetHandleVerifier [0x0x7ff70eaf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
